--- a/apps/elpt/AllUploadFiles_ToolTesting/Utility Bills Template.xlsx
+++ b/apps/elpt/AllUploadFiles_ToolTesting/Utility Bills Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ucdavis-shinyr\apps\elpt\AllUploadFiles_ToolTesting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\btuser\Documents\GitHub\IAC-Decarb-Tools-Dev\apps\elpt\AllUploadFiles_ToolTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B90DB-2D68-42A6-AB28-39DC0AF2CA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC88CCE-7E1F-485C-BA89-2319A4549007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tool template" sheetId="1" r:id="rId1"/>
@@ -1282,17 +1282,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,9 +1306,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>5</v>
@@ -1324,9 +1324,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>6</v>
@@ -1338,9 +1338,9 @@
         <v>1270.9499999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -1352,9 +1352,9 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>8</v>
@@ -1366,9 +1366,9 @@
         <v>1253.6999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>10</v>
@@ -1389,9 +1389,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>12</v>
@@ -1412,9 +1412,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>14</v>
@@ -1435,9 +1435,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>15</v>
@@ -1458,9 +1458,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>16</v>
@@ -1473,9 +1473,9 @@
       </c>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1487,9 +1487,9 @@
         <v>1277.25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>18</v>
@@ -1501,9 +1501,9 @@
         <v>1233.3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>4</v>
@@ -1515,7 +1515,7 @@
         <v>1232.25</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B108" s="4">
         <v>0</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B109" s="4">
         <v>4.1666666666666699E-2</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B110" s="4">
         <v>8.3333333333333301E-2</v>
       </c>
@@ -1542,181 +1542,181 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B111" s="4">
         <v>0.125</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B112" s="4">
         <v>0.16666666666666699</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B113" s="4">
         <v>0.20833333333333301</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B114" s="4">
         <v>0.25</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B115" s="4">
         <v>0.29166666666666702</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B116" s="4">
         <v>0.33333333333333298</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B117" s="4">
         <v>0.375</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <v>0.41666666666666702</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B119" s="4">
         <v>0.45833333333333298</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B120" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B121" s="4">
         <v>0.54166666666666696</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B122" s="4">
         <v>0.58333333333333304</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B123" s="4">
         <v>0.625</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B124" s="4">
         <v>0.66666666666666696</v>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B125" s="4">
         <v>0.70833333333333304</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B126" s="4">
         <v>0.75</v>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B127" s="4">
         <v>0.79166666666666696</v>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B128" s="4">
         <v>0.83333333333333304</v>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B129" s="4">
         <v>0.875</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B130" s="4">
         <v>0.91666666666666696</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B131" s="4">
         <v>0.95833333333333304</v>
       </c>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B132" s="4"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B133" s="4"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B134" s="4"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B135" s="4"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B136" s="4"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B137" s="4"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B138" s="4"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B139" s="4"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B140" s="4"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B141" s="4"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B142" s="4"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B143" s="4"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B144" s="4"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B145" s="4"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B146" s="4"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B147" s="4"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B148" s="4"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B149" s="4"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B150" s="4"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B151" s="4"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B152" s="4"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B153" s="4"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B154" s="4"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B155" s="4"/>
     </row>
   </sheetData>
